--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008520536396819937</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48177022</v>
+        <v>4033327</v>
       </c>
       <c r="L2" t="n">
-        <v>25287133</v>
+        <v>1655598</v>
       </c>
       <c r="M2" t="n">
-        <v>5865647</v>
+        <v>310192</v>
       </c>
       <c r="N2" t="n">
-        <v>279297</v>
+        <v>5963</v>
       </c>
       <c r="O2" t="n">
-        <v>3371210</v>
+        <v>149576</v>
       </c>
       <c r="P2" t="n">
-        <v>1311859</v>
+        <v>42938</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999873638153076</v>
+        <v>0.9999811053276062</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8333895802497864</v>
+        <v>0.717011570930481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7048232555389404</v>
+        <v>0.5339586138725281</v>
       </c>
       <c r="T2" t="n">
-        <v>0.636003315448761</v>
+        <v>0.4001227915287018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2121231257915497</v>
+        <v>0.03960336744785309</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6887218356132507</v>
+        <v>0.4338504076004028</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7975190281867981</v>
+        <v>0.5871943831443787</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002039522590464157</v>
       </c>
       <c r="C3" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>48177022</v>
+        <v>4033327</v>
       </c>
       <c r="E3" t="n">
-        <v>7010620</v>
+        <v>909028</v>
       </c>
       <c r="F3" t="n">
-        <v>210123</v>
+        <v>39519</v>
       </c>
       <c r="G3" t="n">
-        <v>22998</v>
+        <v>3895</v>
       </c>
       <c r="H3" t="n">
-        <v>12729</v>
+        <v>2622</v>
       </c>
       <c r="I3" t="n">
-        <v>1009</v>
+        <v>307</v>
       </c>
       <c r="J3" t="n">
-        <v>110764938</v>
+        <v>10069500</v>
       </c>
       <c r="K3" t="n">
-        <v>115509919</v>
+        <v>9835422</v>
       </c>
       <c r="L3" t="n">
-        <v>133692640</v>
+        <v>11631081</v>
       </c>
       <c r="M3" t="n">
-        <v>166909122</v>
+        <v>15006567</v>
       </c>
       <c r="N3" t="n">
-        <v>178553168</v>
+        <v>16181288</v>
       </c>
       <c r="O3" t="n">
-        <v>173438172</v>
+        <v>15708234</v>
       </c>
       <c r="P3" t="n">
-        <v>178114389</v>
+        <v>16191882</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8690789341926575</v>
+        <v>0.8084903359413147</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6967452764511108</v>
+        <v>0.4957019686698914</v>
       </c>
       <c r="T3" t="n">
-        <v>0.568935751914978</v>
+        <v>0.3284599483013153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2834193408489227</v>
+        <v>0.0661768764257431</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6004835367202759</v>
+        <v>0.2918111979961395</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6163172721862793</v>
+        <v>0.2214075028896332</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03216441684267991</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>8882403</v>
+        <v>1421742</v>
       </c>
       <c r="E4" t="n">
-        <v>25287133</v>
+        <v>1655598</v>
       </c>
       <c r="F4" t="n">
-        <v>1779290</v>
+        <v>210650</v>
       </c>
       <c r="G4" t="n">
-        <v>142483</v>
+        <v>21665</v>
       </c>
       <c r="H4" t="n">
-        <v>182197</v>
+        <v>27177</v>
       </c>
       <c r="I4" t="n">
-        <v>19664</v>
+        <v>3055</v>
       </c>
       <c r="J4" t="n">
-        <v>882</v>
+        <v>120</v>
       </c>
       <c r="K4" t="n">
-        <v>9631504</v>
+        <v>1591864</v>
       </c>
       <c r="L4" t="n">
-        <v>10590134</v>
+        <v>1445013</v>
       </c>
       <c r="M4" t="n">
-        <v>3357020</v>
+        <v>465050</v>
       </c>
       <c r="N4" t="n">
-        <v>1037377</v>
+        <v>144605</v>
       </c>
       <c r="O4" t="n">
-        <v>1523669</v>
+        <v>195188</v>
       </c>
       <c r="P4" t="n">
-        <v>333066</v>
+        <v>30186</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999936819076538</v>
+        <v>0.9999905228614807</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8508601784706116</v>
+        <v>0.7600081562995911</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7007610201835632</v>
+        <v>0.5141196250915527</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6006029844284058</v>
+        <v>0.3607670068740845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2426423579454422</v>
+        <v>0.04955229908227921</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6415830254554749</v>
+        <v>0.3489295840263367</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6953064799308777</v>
+        <v>0.3215655386447906</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>538157</v>
+        <v>126088</v>
       </c>
       <c r="E5" t="n">
-        <v>2887539</v>
+        <v>397670</v>
       </c>
       <c r="F5" t="n">
-        <v>5865647</v>
+        <v>310192</v>
       </c>
       <c r="G5" t="n">
-        <v>315001</v>
+        <v>36925</v>
       </c>
       <c r="H5" t="n">
-        <v>631739</v>
+        <v>64142</v>
       </c>
       <c r="I5" t="n">
-        <v>71715</v>
+        <v>9355</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7257555</v>
+        <v>955387</v>
       </c>
       <c r="L5" t="n">
-        <v>11006093</v>
+        <v>1684308</v>
       </c>
       <c r="M5" t="n">
-        <v>4444211</v>
+        <v>634191</v>
       </c>
       <c r="N5" t="n">
-        <v>706158</v>
+        <v>84144</v>
       </c>
       <c r="O5" t="n">
-        <v>2242949</v>
+        <v>363002</v>
       </c>
       <c r="P5" t="n">
-        <v>816686</v>
+        <v>150994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999951124191284</v>
+        <v>0.9999926686286926</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9064711928367615</v>
+        <v>0.8448312282562256</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8804036974906921</v>
+        <v>0.8093737363815308</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9567980766296387</v>
+        <v>0.9330384135246277</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9903445839881897</v>
+        <v>0.9860655069351196</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9791411161422729</v>
+        <v>0.9659972190856934</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9936328530311584</v>
+        <v>0.9889631867408752</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>156052</v>
+        <v>23565</v>
       </c>
       <c r="E6" t="n">
-        <v>213545</v>
+        <v>26993</v>
       </c>
       <c r="F6" t="n">
-        <v>238985</v>
+        <v>25838</v>
       </c>
       <c r="G6" t="n">
-        <v>279297</v>
+        <v>5963</v>
       </c>
       <c r="H6" t="n">
-        <v>87070</v>
+        <v>6875</v>
       </c>
       <c r="I6" t="n">
-        <v>10370</v>
+        <v>850</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>229</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>51870</v>
+        <v>18899</v>
       </c>
       <c r="E7" t="n">
-        <v>435363</v>
+        <v>99279</v>
       </c>
       <c r="F7" t="n">
-        <v>1034696</v>
+        <v>162808</v>
       </c>
       <c r="G7" t="n">
-        <v>490483</v>
+        <v>65375</v>
       </c>
       <c r="H7" t="n">
-        <v>3371210</v>
+        <v>149576</v>
       </c>
       <c r="I7" t="n">
-        <v>230308</v>
+        <v>16619</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>3022</v>
+        <v>1570</v>
       </c>
       <c r="E8" t="n">
-        <v>43067</v>
+        <v>12043</v>
       </c>
       <c r="F8" t="n">
-        <v>93926</v>
+        <v>26235</v>
       </c>
       <c r="G8" t="n">
-        <v>66412</v>
+        <v>16745</v>
       </c>
       <c r="H8" t="n">
-        <v>609934</v>
+        <v>94372</v>
       </c>
       <c r="I8" t="n">
-        <v>1311859</v>
+        <v>42938</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
